--- a/samples/OutputExample.xlsx
+++ b/samples/OutputExample.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\github-workspace\Athletic-MoushiCommu-Excel\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\github-workspace\Athletic-MoushiCommu-Excel\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BA436D-8E9B-49AD-986B-A7D2B0CC2965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BC39B70-F51E-4CD1-A79C-3134C2753870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{930FC441-4A61-4C14-9A47-6E7A0C10006C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{522C7D55-41F4-4814-9FE1-2F2CD103EC58}"/>
   </bookViews>
   <sheets>
-    <sheet name="TeamList_20260705_231945" sheetId="1" r:id="rId1"/>
-    <sheet name="EntryList_20260705_231950" sheetId="2" r:id="rId2"/>
+    <sheet name="TeamList_20260716_234710" sheetId="1" r:id="rId1"/>
+    <sheet name="EntryList_20260716_234752" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,20 +40,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="167">
   <si>
     <t/>
   </si>
   <si>
+    <t>Ｂ</t>
+  </si>
+  <si>
+    <t>識辺　久菜</t>
+  </si>
+  <si>
+    <t>office.orcheria@example.com</t>
+  </si>
+  <si>
+    <t>はい</t>
+  </si>
+  <si>
+    <t>0X0-XXXX-XXXX</t>
+  </si>
+  <si>
+    <t>空野　洋子</t>
+  </si>
+  <si>
+    <t>0953-XX-XXXX</t>
+  </si>
+  <si>
+    <t>空野　誠志郎</t>
+  </si>
+  <si>
+    <t>長崎県長崎市XX町XX　X-XX-XXX</t>
+  </si>
+  <si>
+    <t>長崎県</t>
+  </si>
+  <si>
+    <t>オルケリア</t>
+  </si>
+  <si>
+    <t>Orcheria</t>
+  </si>
+  <si>
+    <t>Orcheria Athlete Club</t>
+  </si>
+  <si>
+    <t>D:\Documents\github-workspace\Athletic-MoushiCommu-Excel\samples\申込書（sample02）.xlsx</t>
+  </si>
+  <si>
     <t>桜川　咲</t>
   </si>
   <si>
     <t>saki.sakuragawa.xxx@example.com</t>
   </si>
   <si>
-    <t>はい</t>
-  </si>
-  <si>
     <t>０X0-XXXX-XXXX</t>
   </si>
   <si>
@@ -66,16 +105,16 @@
     <t>長崎県諫早市XX町X-XX</t>
   </si>
   <si>
-    <t>長崎県</t>
-  </si>
-  <si>
-    <t>Ｍ中</t>
-  </si>
-  <si>
-    <t>諫早市立Ｍ中学校</t>
-  </si>
-  <si>
-    <t>D:\Documents\github-workspace\Athletic-MoushiCommu-Excel\template\申込書（sample01）.xlsx</t>
+    <t>アオゾラチュウ</t>
+  </si>
+  <si>
+    <t>あおぞら中</t>
+  </si>
+  <si>
+    <t>諫早市立あおぞら中学校</t>
+  </si>
+  <si>
+    <t>D:\Documents\github-workspace\Athletic-MoushiCommu-Excel\samples\申込書（sample01）.xlsx</t>
   </si>
   <si>
     <t>審判員３／資格</t>
@@ -135,6 +174,9 @@
     <t>登録陸協</t>
   </si>
   <si>
+    <t>チーム略称カナ</t>
+  </si>
+  <si>
     <t>チーム略称</t>
   </si>
   <si>
@@ -144,6 +186,168 @@
     <t>Source File</t>
   </si>
   <si>
+    <t>女子1500m//</t>
+  </si>
+  <si>
+    <t>トラック</t>
+  </si>
+  <si>
+    <t>4:37.22</t>
+  </si>
+  <si>
+    <t>女子1500m</t>
+  </si>
+  <si>
+    <t>長崎</t>
+  </si>
+  <si>
+    <t>ｵﾙｹﾘｱ</t>
+  </si>
+  <si>
+    <t>中3</t>
+  </si>
+  <si>
+    <t>ｶｻﾞﾊﾅ ｽﾐﾚ</t>
+  </si>
+  <si>
+    <t>風花　菫</t>
+  </si>
+  <si>
+    <t>8121</t>
+  </si>
+  <si>
+    <t>女子</t>
+  </si>
+  <si>
+    <t>Orcheria-5</t>
+  </si>
+  <si>
+    <t>女子400m//</t>
+  </si>
+  <si>
+    <t>57.97</t>
+  </si>
+  <si>
+    <t>女子400m</t>
+  </si>
+  <si>
+    <t>女子棒高跳//</t>
+  </si>
+  <si>
+    <t>フィールド</t>
+  </si>
+  <si>
+    <t>2m90</t>
+  </si>
+  <si>
+    <t>女子棒高跳</t>
+  </si>
+  <si>
+    <t>中1</t>
+  </si>
+  <si>
+    <t>ﾋﾉｼﾀ ﾅﾂ</t>
+  </si>
+  <si>
+    <t>陽ノ下　菜津</t>
+  </si>
+  <si>
+    <t>8104</t>
+  </si>
+  <si>
+    <t>Orcheria-4</t>
+  </si>
+  <si>
+    <t>女子100m//</t>
+  </si>
+  <si>
+    <t>13.27</t>
+  </si>
+  <si>
+    <t>女子100m</t>
+  </si>
+  <si>
+    <t>4:35.13</t>
+  </si>
+  <si>
+    <t>ｲﾁｼﾞｮｳ ﾅｶﾞｾ</t>
+  </si>
+  <si>
+    <t>一条　流星</t>
+  </si>
+  <si>
+    <t>8103</t>
+  </si>
+  <si>
+    <t>Orcheria-3</t>
+  </si>
+  <si>
+    <t>女子800m//</t>
+  </si>
+  <si>
+    <t>2:19.26</t>
+  </si>
+  <si>
+    <t>女子800m</t>
+  </si>
+  <si>
+    <t>1:00.76</t>
+  </si>
+  <si>
+    <t>中2</t>
+  </si>
+  <si>
+    <t>ｼﾙﾍﾞ ｶｶﾞﾘ</t>
+  </si>
+  <si>
+    <t>識辺　佳賀里</t>
+  </si>
+  <si>
+    <t>8102</t>
+  </si>
+  <si>
+    <t>Orcheria-2</t>
+  </si>
+  <si>
+    <t>女子200m//</t>
+  </si>
+  <si>
+    <t>26.82</t>
+  </si>
+  <si>
+    <t>女子200m</t>
+  </si>
+  <si>
+    <t>女子走幅跳//</t>
+  </si>
+  <si>
+    <t>5m18</t>
+  </si>
+  <si>
+    <t>女子走幅跳</t>
+  </si>
+  <si>
+    <t>ｿﾗﾉ ﾐﾅﾓ</t>
+  </si>
+  <si>
+    <t>空野　みなも</t>
+  </si>
+  <si>
+    <t>8101</t>
+  </si>
+  <si>
+    <t>Orcheria-1</t>
+  </si>
+  <si>
+    <t>女子300mH//</t>
+  </si>
+  <si>
+    <t>51.84</t>
+  </si>
+  <si>
+    <t>女子300mH</t>
+  </si>
+  <si>
     <t>女子4×100mR//</t>
   </si>
   <si>
@@ -156,7 +360,7 @@
     <t>女子4×100mR</t>
   </si>
   <si>
-    <t>長崎</t>
+    <t>ｱｵｿﾞﾗﾁｭｳ</t>
   </si>
   <si>
     <t>1</t>
@@ -171,18 +375,12 @@
     <t>2135</t>
   </si>
   <si>
-    <t>女子</t>
-  </si>
-  <si>
-    <t>Ｍ中-5</t>
+    <t>あおぞら中-5</t>
   </si>
   <si>
     <t>女子円盤投//</t>
   </si>
   <si>
-    <t>フィールド</t>
-  </si>
-  <si>
     <t>32m59</t>
   </si>
   <si>
@@ -210,30 +408,15 @@
     <t>2134</t>
   </si>
   <si>
-    <t>Ｍ中-4</t>
-  </si>
-  <si>
-    <t>女子800m//</t>
-  </si>
-  <si>
-    <t>トラック</t>
+    <t>あおぞら中-4</t>
   </si>
   <si>
     <t>2:27.49</t>
   </si>
   <si>
-    <t>女子800m</t>
-  </si>
-  <si>
-    <t>女子1500m//</t>
-  </si>
-  <si>
     <t>4:52.75</t>
   </si>
   <si>
-    <t>女子1500m</t>
-  </si>
-  <si>
     <t>ｽｽﾞﾑﾗ ｻﾝｺﾞ</t>
   </si>
   <si>
@@ -243,18 +426,12 @@
     <t>2133</t>
   </si>
   <si>
-    <t>Ｍ中-3</t>
-  </si>
-  <si>
-    <t>女子300mH//</t>
+    <t>あおぞら中-3</t>
   </si>
   <si>
     <t>51.32</t>
   </si>
   <si>
-    <t>女子300mH</t>
-  </si>
-  <si>
     <t>4:48.17</t>
   </si>
   <si>
@@ -270,27 +447,15 @@
     <t>2132</t>
   </si>
   <si>
-    <t>Ｍ中-2</t>
-  </si>
-  <si>
-    <t>女子走幅跳//</t>
+    <t>あおぞら中-2</t>
   </si>
   <si>
     <t>5m08</t>
   </si>
   <si>
-    <t>女子走幅跳</t>
-  </si>
-  <si>
-    <t>女子400m//</t>
-  </si>
-  <si>
     <t>1:04.15</t>
   </si>
   <si>
-    <t>女子400m</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -303,7 +468,7 @@
     <t>2131</t>
   </si>
   <si>
-    <t>Ｍ中-1</t>
+    <t>あおぞら中-1</t>
   </si>
   <si>
     <t>4:27.53</t>
@@ -785,150 +950,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F168212F-B9DF-4E34-9E16-7A7841FB8445}">
-  <dimension ref="A1:V2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCECAAE-A372-43EA-BCD3-9C4D7FC5316F}">
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="98" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="97.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="15.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="G2" s="2">
+        <v>46208</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="L2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>10500</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>5</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46208</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>10500</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>0</v>
@@ -940,6 +1109,80 @@
         <v>0</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46209</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>9000</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>6</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -950,20 +1193,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C7D287-85A3-404E-8D6A-84DF88A825E1}">
-  <dimension ref="A1:W16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F079C86-E77E-4FA9-928E-33F91B2B8CB8}">
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="98" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="97.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="5.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.25" bestFit="1" customWidth="1"/>
@@ -977,87 +1223,87 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>106</v>
+        <v>161</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1066,34 +1312,37 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="J2" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="L2" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>106</v>
       </c>
       <c r="N2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2">
-        <v>40862</v>
+        <v>40831</v>
       </c>
       <c r="P2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="S2">
         <v>900</v>
@@ -1102,10 +1351,10 @@
         <v>18</v>
       </c>
       <c r="U2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="V2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="W2">
         <v>-13122.999999999998</v>
@@ -1113,16 +1362,16 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1131,34 +1380,37 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="L3" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>106</v>
       </c>
       <c r="N3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O3" s="2">
-        <v>40862</v>
+        <v>40831</v>
       </c>
       <c r="P3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="S3">
         <v>900</v>
@@ -1167,10 +1419,10 @@
         <v>19</v>
       </c>
       <c r="U3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="V3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="W3">
         <v>-26752.999999999996</v>
@@ -1178,16 +1430,16 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1196,34 +1448,37 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="L4" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>106</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O4" s="2">
-        <v>40862</v>
+        <v>40831</v>
       </c>
       <c r="P4" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="S4">
         <v>1500</v>
@@ -1232,10 +1487,10 @@
         <v>22</v>
       </c>
       <c r="U4" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="V4" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="W4">
         <v>-5309.0000000000009</v>
@@ -1243,16 +1498,16 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1261,34 +1516,37 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="L5" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>106</v>
       </c>
       <c r="N5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O5" s="2">
         <v>41234</v>
       </c>
       <c r="P5" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="S5">
         <v>900</v>
@@ -1297,10 +1555,10 @@
         <v>17</v>
       </c>
       <c r="U5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="V5" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="W5">
         <v>-6415.0000000000009</v>
@@ -1308,16 +1566,16 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1326,34 +1584,37 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="I6" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="L6" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>106</v>
       </c>
       <c r="N6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O6" s="2">
         <v>41234</v>
       </c>
       <c r="P6" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="S6">
         <v>900</v>
@@ -1362,10 +1623,10 @@
         <v>25</v>
       </c>
       <c r="U6" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="V6" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="W6">
         <v>508</v>
@@ -1373,16 +1634,16 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -1391,34 +1652,37 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="L7" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>106</v>
       </c>
       <c r="N7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O7" s="2">
         <v>41234</v>
       </c>
       <c r="P7" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1427,10 +1691,10 @@
         <v>22</v>
       </c>
       <c r="U7" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="V7" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="W7">
         <v>-5309.0000000000009</v>
@@ -1438,16 +1702,16 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1456,34 +1720,37 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>106</v>
       </c>
       <c r="N8" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O8" s="2">
-        <v>41425</v>
+        <v>41403</v>
       </c>
       <c r="P8" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="S8">
         <v>900</v>
@@ -1492,10 +1759,10 @@
         <v>19</v>
       </c>
       <c r="U8" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="V8" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="W8">
         <v>-28817</v>
@@ -1503,16 +1770,16 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1521,34 +1788,37 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="I9" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>106</v>
       </c>
       <c r="N9" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O9" s="2">
-        <v>41425</v>
+        <v>41403</v>
       </c>
       <c r="P9" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="S9">
         <v>900</v>
@@ -1557,10 +1827,10 @@
         <v>21</v>
       </c>
       <c r="U9" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="V9" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="W9">
         <v>-5132</v>
@@ -1568,16 +1838,16 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -1586,34 +1856,37 @@
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="I10" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>106</v>
       </c>
       <c r="N10" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O10" s="2">
-        <v>41425</v>
+        <v>41403</v>
       </c>
       <c r="P10" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1622,10 +1895,10 @@
         <v>22</v>
       </c>
       <c r="U10" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="V10" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="W10">
         <v>-5309.0000000000009</v>
@@ -1633,16 +1906,16 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1651,34 +1924,37 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="I11" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L11" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>106</v>
       </c>
       <c r="N11" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O11" s="2">
         <v>41455</v>
       </c>
       <c r="P11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="S11">
         <v>900</v>
@@ -1687,10 +1963,10 @@
         <v>19</v>
       </c>
       <c r="U11" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="V11" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="W11">
         <v>-29275</v>
@@ -1698,16 +1974,16 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1716,34 +1992,37 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="I12" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>106</v>
       </c>
       <c r="N12" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O12" s="2">
         <v>41455</v>
       </c>
       <c r="P12" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="S12">
         <v>900</v>
@@ -1752,10 +2031,10 @@
         <v>18</v>
       </c>
       <c r="U12" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="V12" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="W12">
         <v>-14749.000000000002</v>
@@ -1763,16 +2042,16 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1781,34 +2060,37 @@
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="I13" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="J13" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L13" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>106</v>
       </c>
       <c r="N13" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O13" s="2">
         <v>41455</v>
       </c>
       <c r="P13" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1817,10 +2099,10 @@
         <v>22</v>
       </c>
       <c r="U13" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="V13" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="W13">
         <v>-5309.0000000000009</v>
@@ -1828,16 +2110,16 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1846,34 +2128,37 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="I14" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J14" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L14" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>106</v>
       </c>
       <c r="N14" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O14" s="2">
         <v>41487</v>
       </c>
       <c r="P14" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="S14">
         <v>900</v>
@@ -1882,10 +2167,10 @@
         <v>28</v>
       </c>
       <c r="U14" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="V14" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="W14">
         <v>2739</v>
@@ -1893,16 +2178,16 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1911,34 +2196,37 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="I15" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J15" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
+        <v>106</v>
       </c>
       <c r="N15" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O15" s="2">
         <v>41487</v>
       </c>
       <c r="P15" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="S15">
         <v>900</v>
@@ -1947,10 +2235,10 @@
         <v>27</v>
       </c>
       <c r="U15" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="V15" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="W15">
         <v>3259.0000000000005</v>
@@ -1958,16 +2246,16 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1976,34 +2264,37 @@
         <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="I16" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J16" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="M16" t="s">
+        <v>106</v>
       </c>
       <c r="N16" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O16" s="2">
         <v>41487</v>
       </c>
       <c r="P16" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2012,13 +2303,693 @@
         <v>22</v>
       </c>
       <c r="U16" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="V16" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="W16">
         <v>-5309.0000000000009</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" t="s">
+        <v>95</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L17" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" t="s">
+        <v>52</v>
+      </c>
+      <c r="O17" s="2">
+        <v>41093</v>
+      </c>
+      <c r="P17" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>900</v>
+      </c>
+      <c r="T17">
+        <v>21</v>
+      </c>
+      <c r="U17" t="s">
+        <v>49</v>
+      </c>
+      <c r="V17" t="s">
+        <v>99</v>
+      </c>
+      <c r="W17">
+        <v>-5184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s">
+        <v>95</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L18" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" t="s">
+        <v>52</v>
+      </c>
+      <c r="O18" s="2">
+        <v>41093</v>
+      </c>
+      <c r="P18" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="S18">
+        <v>900</v>
+      </c>
+      <c r="T18">
+        <v>25</v>
+      </c>
+      <c r="U18" t="s">
+        <v>64</v>
+      </c>
+      <c r="V18" t="s">
+        <v>92</v>
+      </c>
+      <c r="W18">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" t="s">
+        <v>52</v>
+      </c>
+      <c r="O19" s="2">
+        <v>41129</v>
+      </c>
+      <c r="P19" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S19">
+        <v>900</v>
+      </c>
+      <c r="T19">
+        <v>16</v>
+      </c>
+      <c r="U19" t="s">
+        <v>49</v>
+      </c>
+      <c r="V19" t="s">
+        <v>89</v>
+      </c>
+      <c r="W19">
+        <v>-2682</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L20" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" t="s">
+        <v>52</v>
+      </c>
+      <c r="O20" s="2">
+        <v>41129</v>
+      </c>
+      <c r="P20" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S20">
+        <v>900</v>
+      </c>
+      <c r="T20">
+        <v>17</v>
+      </c>
+      <c r="U20" t="s">
+        <v>49</v>
+      </c>
+      <c r="V20" t="s">
+        <v>60</v>
+      </c>
+      <c r="W20">
+        <v>-6076</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" t="s">
+        <v>12</v>
+      </c>
+      <c r="M21" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" t="s">
+        <v>52</v>
+      </c>
+      <c r="O21" s="2">
+        <v>41568</v>
+      </c>
+      <c r="P21" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S21">
+        <v>900</v>
+      </c>
+      <c r="T21">
+        <v>18</v>
+      </c>
+      <c r="U21" t="s">
+        <v>49</v>
+      </c>
+      <c r="V21" t="s">
+        <v>80</v>
+      </c>
+      <c r="W21">
+        <v>-13925.999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" t="s">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L22" t="s">
+        <v>12</v>
+      </c>
+      <c r="M22" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" t="s">
+        <v>52</v>
+      </c>
+      <c r="O22" s="2">
+        <v>41568</v>
+      </c>
+      <c r="P22" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S22">
+        <v>900</v>
+      </c>
+      <c r="T22">
+        <v>19</v>
+      </c>
+      <c r="U22" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" t="s">
+        <v>48</v>
+      </c>
+      <c r="W22">
+        <v>-27513</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" t="s">
+        <v>69</v>
+      </c>
+      <c r="J23" t="s">
+        <v>68</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" t="s">
+        <v>53</v>
+      </c>
+      <c r="N23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O23" s="2">
+        <v>41222</v>
+      </c>
+      <c r="P23" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S23">
+        <v>900</v>
+      </c>
+      <c r="T23">
+        <v>15</v>
+      </c>
+      <c r="U23" t="s">
+        <v>49</v>
+      </c>
+      <c r="V23" t="s">
+        <v>72</v>
+      </c>
+      <c r="W23">
+        <v>-1327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" t="s">
+        <v>68</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" t="s">
+        <v>52</v>
+      </c>
+      <c r="O24" s="2">
+        <v>41222</v>
+      </c>
+      <c r="P24" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S24">
+        <v>900</v>
+      </c>
+      <c r="T24">
+        <v>24</v>
+      </c>
+      <c r="U24" t="s">
+        <v>64</v>
+      </c>
+      <c r="V24" t="s">
+        <v>63</v>
+      </c>
+      <c r="W24">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>58</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" t="s">
+        <v>55</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" t="s">
+        <v>52</v>
+      </c>
+      <c r="O25" s="2">
+        <v>40960</v>
+      </c>
+      <c r="P25" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S25">
+        <v>900</v>
+      </c>
+      <c r="T25">
+        <v>17</v>
+      </c>
+      <c r="U25" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" t="s">
+        <v>60</v>
+      </c>
+      <c r="W25">
+        <v>-5796.9999999999991</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" t="s">
+        <v>12</v>
+      </c>
+      <c r="M26" t="s">
+        <v>53</v>
+      </c>
+      <c r="N26" t="s">
+        <v>52</v>
+      </c>
+      <c r="O26" s="2">
+        <v>40960</v>
+      </c>
+      <c r="P26" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S26">
+        <v>900</v>
+      </c>
+      <c r="T26">
+        <v>19</v>
+      </c>
+      <c r="U26" t="s">
+        <v>49</v>
+      </c>
+      <c r="V26" t="s">
+        <v>48</v>
+      </c>
+      <c r="W26">
+        <v>-27722.000000000004</v>
       </c>
     </row>
   </sheetData>
